--- a/agriculture 4.xlsx
+++ b/agriculture 4.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate of APY Statistics of Foodgrains in India</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -281,7 +278,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -303,14 +300,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -392,20 +381,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -417,7 +402,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,1060 +423,1048 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="n">
+        <v>-0.369913686806411</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2.30224321133412</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2.68293150002872</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>-0.369913686806411</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>2.30224321133412</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>2.68293150002872</v>
+      <c r="B4" s="4" t="n">
+        <v>5.29084158415842</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>13.8680515483747</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8.1462140992167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>5.29084158415842</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>13.8680515483747</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8.1462140992167</v>
+      <c r="B5" s="4" t="n">
+        <v>6.83710451562345</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>17.9391891891892</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>10.3918052010761</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>6.83710451562345</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>17.9391891891892</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>10.3918052010761</v>
+      <c r="B6" s="4" t="n">
+        <v>-1.10937929769872</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-2.56373531939271</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-1.46999093948198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>-1.10937929769872</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>-2.56373531939271</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>-1.46999093948198</v>
+      <c r="B7" s="4" t="n">
+        <v>2.50324494715373</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-1.73452888431576</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-4.13489131641115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>2.50324494715373</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>-1.73452888431576</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>-4.13489131641115</v>
+      <c r="B8" s="4" t="n">
+        <v>0.524602026049204</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>4.50261780104713</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3.95766145704128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>0.524602026049204</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>4.50261780104713</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>3.95766145704128</v>
+      <c r="B9" s="4" t="n">
+        <v>-1.49361166096814</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-7.94446034926997</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-6.54968341340801</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>-1.49361166096814</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>-7.94446034926997</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>-6.54968341340801</v>
+      <c r="B10" s="4" t="n">
+        <v>4.82279868469127</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>19.9502410200591</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>14.4328492875504</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>4.82279868469127</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>19.9502410200591</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>14.4328492875504</v>
+      <c r="B11" s="4" t="n">
+        <v>0.923666782851162</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-0.609281825252783</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-1.51891578274</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>0.923666782851162</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>-0.609281825252783</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>-1.51891578274</v>
+      <c r="B12" s="4" t="n">
+        <v>-0.207218097047135</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>6.97795748010954</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>7.19961328136802</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>-0.207218097047135</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>6.97795748010954</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>7.19961328136802</v>
+      <c r="B13" s="4" t="n">
+        <v>1.42758262675204</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.84125822970007</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-0.577757736317008</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>1.42758262675204</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.84125822970007</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>-0.577757736317008</v>
+      <c r="B14" s="4" t="n">
+        <v>0.520344621683866</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-3.09515173497762</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-3.59724466366188</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>0.520344621683866</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>-3.09515173497762</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>-3.59724466366188</v>
+      <c r="B15" s="4" t="n">
+        <v>-0.356415478615069</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.611353711790397</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.971830157609976</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>-0.356415478615069</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.611353711790397</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0.971830157609976</v>
+      <c r="B16" s="4" t="n">
+        <v>0.58763413387839</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>10.8134920634921</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>10.1649751736389</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>0.58763413387839</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>10.8134920634921</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>10.1649751736389</v>
+      <c r="B17" s="4" t="n">
+        <v>-2.54847176361019</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-19.0353625783348</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-16.9182373311481</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>-2.54847176361019</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>-19.0353625783348</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>-16.9182373311481</v>
+      <c r="B18" s="4" t="n">
+        <v>0.17376194613381</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>2.59847961299242</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2.42133061821883</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>0.17376194613381</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2.59847961299242</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2.42133061821883</v>
+      <c r="B19" s="4" t="n">
+        <v>5.30789245446661</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>28.0479590462077</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>21.5936626281454</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>5.30789245446661</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>28.0479590462077</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>21.5936626281454</v>
+      <c r="B20" s="4" t="n">
+        <v>-0.815351671882714</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-1.09416096791162</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-0.281035231598581</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>-0.815351671882714</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>-1.09416096791162</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>-0.281035231598581</v>
+      <c r="B21" s="4" t="n">
+        <v>2.60732375653905</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>5.83980427614084</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>3.15006020855217</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>2.60732375653905</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>5.83980427614084</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>3.15006020855217</v>
+      <c r="B22" s="4" t="n">
+        <v>0.606943432872065</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>8.96482412060302</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>8.30714968765911</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>0.606943432872065</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>8.96482412060302</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>8.30714968765911</v>
+      <c r="B23" s="4" t="n">
+        <v>-1.36743886743886</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-2.99760191846523</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-1.65233344799908</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>-1.36743886743886</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>-2.99760191846523</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>-1.65233344799908</v>
+      <c r="B24" s="4" t="n">
+        <v>-2.72386233893329</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-7.73984976704384</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-5.15687486154671</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>-2.72386233893329</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>-7.73984976704384</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>-5.15687486154671</v>
+      <c r="B25" s="4" t="n">
+        <v>6.08651911468814</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>7.8738534473874</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1.68539325842696</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>6.08651911468814</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>7.8738534473874</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1.68539325842696</v>
+      <c r="B26" s="4" t="n">
+        <v>-4.31484115694643</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-4.62405655870832</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-0.322787335130625</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>-4.31484115694643</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>-4.62405655870832</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>-0.322787335130625</v>
+      <c r="B27" s="4" t="n">
+        <v>5.86389164188967</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>21.236101372333</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>14.5203153426319</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>5.86389164188967</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>21.236101372333</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>14.5203153426319</v>
+      <c r="B28" s="4" t="n">
+        <v>-2.98018411608676</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-8.14674047756755</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-5.32503018364364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>-2.98018411608676</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>-8.14674047756755</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>-5.32503018364364</v>
+      <c r="B29" s="4" t="n">
+        <v>2.54100997105178</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>13.7087343707835</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>10.8911112602635</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>2.54100997105178</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>13.7087343707835</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>10.8911112602635</v>
+      <c r="B30" s="4" t="n">
+        <v>1.16844416562107</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>4.34301083775019</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>3.13729446181781</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>1.16844416562107</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>4.34301083775019</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>3.13729446181781</v>
+      <c r="B31" s="4" t="n">
+        <v>-2.94550810014728</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-16.8309325246399</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-14.3065336463224</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>-2.94550810014728</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>-16.8309325246399</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>-14.3065336463224</v>
+      <c r="B32" s="4" t="n">
+        <v>1.16604105103426</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>18.1312670920693</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>16.769200917672</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>1.16604105103426</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>18.1312670920693</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>16.769200917672</v>
+      <c r="B33" s="4" t="n">
+        <v>1.94994868556089</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2.86287522185353</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.895361908020154</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>1.94994868556089</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>2.86287522185353</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.895361908020154</v>
+      <c r="B34" s="4" t="n">
+        <v>-3.12838779619018</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-2.83570892723181</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.302264074170933</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>-3.12838779619018</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>-2.83570892723181</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0.302264074170933</v>
+      <c r="B35" s="4" t="n">
+        <v>4.84412470023981</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>17.642063001853</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>12.2067360165358</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>4.84412470023981</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>17.642063001853</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>12.2067360165358</v>
+      <c r="B36" s="4" t="n">
+        <v>-3.42329978652027</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-4.48250968038328</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-1.0966592350931</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>-3.42329978652027</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>-4.48250968038328</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>-1.0966592350931</v>
+      <c r="B37" s="4" t="n">
+        <v>1.06576142733086</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>3.3667720214374</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>2.27682184913445</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>1.06576142733086</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>3.3667720214374</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>2.27682184913445</v>
+      <c r="B38" s="4" t="n">
+        <v>-0.640524917981566</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>-4.66631215102367</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-4.05146664624341</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>-0.640524917981566</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>-4.66631215102367</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>-4.05146664624341</v>
+      <c r="B39" s="4" t="n">
+        <v>-5.90408805031447</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-2.14056616929298</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>3.99904214559386</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="5" t="n">
-        <v>-5.90408805031447</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>-2.14056616929298</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>3.99904214559386</v>
+      <c r="B40" s="4" t="n">
+        <v>6.66722366112458</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>21.0687566797292</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>13.5015051892786</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>6.66722366112458</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>21.0687566797292</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>13.5015051892786</v>
+      <c r="B41" s="4" t="n">
+        <v>-0.704942429701583</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0.659133709981163</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1.37422704424726</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>-0.704942429701583</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>0.659133709981163</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>1.37422704424726</v>
+      <c r="B42" s="4" t="n">
+        <v>0.844048276406095</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>3.12792329279701</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>2.26427120855013</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>0.844048276406095</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>3.12792329279701</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>2.26427120855013</v>
+      <c r="B43" s="4" t="n">
+        <v>-4.66989987484355</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>-4.5410737570157</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0.135529834682591</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>-4.66989987484355</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>-4.5410737570157</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>0.135529834682591</v>
+      <c r="B44" s="4" t="n">
+        <v>1.05029949946664</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>6.59223185651503</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>5.48406241857502</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>1.05029949946664</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>6.59223185651503</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>5.48406241857502</v>
+      <c r="B45" s="4" t="n">
+        <v>-0.324807145757211</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>2.66324938711835</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>2.99778373964772</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>-0.324807145757211</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>2.66324938711835</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>2.99778373964772</v>
+      <c r="B46" s="4" t="n">
+        <v>0.90427698574338</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>3.92923043525453</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>2.99780161215109</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>0.90427698574338</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>3.92923043525453</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>2.99780161215109</v>
+      <c r="B47" s="4" t="n">
+        <v>-2.30098498304537</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>-5.78590078328982</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>-3.56703964814694</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>-2.30098498304537</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>-5.78590078328982</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>-3.56703964814694</v>
+      <c r="B48" s="4" t="n">
+        <v>2.1237914221965</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>9.92683737944797</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>7.64948522753948</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>2.1237914221965</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>9.92683737944797</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>7.64948522753948</v>
+      <c r="B49" s="4" t="n">
+        <v>0.396504288719846</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>-3.06055563959059</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-3.44797507788162</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>0.396504288719846</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>-3.06055563959059</v>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>-3.44797507788162</v>
+      <c r="B50" s="4" t="n">
+        <v>0.886596276295637</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>5.90346405908666</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>4.96947717563854</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>0.886596276295637</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>5.90346405908666</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>4.96947717563854</v>
+      <c r="B51" s="4" t="n">
+        <v>-1.65375089877767</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>3.04012573056334</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>4.75388370105798</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>-1.65375089877767</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>3.04012573056334</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>4.75388370105798</v>
+      <c r="B52" s="4" t="n">
+        <v>-1.66531275385865</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>-6.19161105815063</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>-4.5774647887324</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>-1.66531275385865</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>-6.19161105815063</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>-4.5774647887324</v>
+      <c r="B53" s="4" t="n">
+        <v>1.42916150351096</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>8.14999237843606</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>6.64206642066421</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>1.42916150351096</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>8.14999237843606</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>6.64206642066421</v>
+      <c r="B54" s="4" t="n">
+        <v>-7.26502687734159</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>-17.8905332393704</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>-11.4763552479815</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>-7.26502687734159</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>-17.8905332393704</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>-11.4763552479815</v>
+      <c r="B55" s="4" t="n">
+        <v>8.42262427542597</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>21.9831778909424</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>12.5081433224756</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="5" t="n">
-        <v>8.42262427542597</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>21.9831778909424</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>12.5081433224756</v>
+      <c r="B56" s="4" t="n">
+        <v>-2.72985014175781</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>-6.95623622121112</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>-4.34279096699479</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>-2.72985014175781</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>-6.95623622121112</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>-4.34279096699479</v>
+      <c r="B57" s="4" t="n">
+        <v>1.26582278481013</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>5.16233111514417</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>3.81355932203389</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="5" t="n">
-        <v>1.26582278481013</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>5.16233111514417</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>3.81355932203389</v>
+      <c r="B58" s="4" t="n">
+        <v>1.73519736842105</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>4.16107382550337</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>2.39067055393587</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="5" t="n">
-        <v>1.73519736842105</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>4.16107382550337</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>2.39067055393587</v>
+      <c r="B59" s="4" t="n">
+        <v>0.291003152534142</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>6.21318114874816</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>5.90831435079726</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>0.291003152534142</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>6.21318114874816</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>5.90831435079726</v>
+      <c r="B60" s="4" t="n">
+        <v>-0.99943580236963</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>1.5989253834821</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>2.64820540395214</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="5" t="n">
-        <v>-0.99943580236963</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>1.5989253834821</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>2.64820540395214</v>
+      <c r="B61" s="4" t="n">
+        <v>-1.22120003256534</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>-6.97743847827014</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>-5.81456259821896</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="5" t="n">
-        <v>-1.22120003256534</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>-6.97743847827014</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>-5.81456259821896</v>
+      <c r="B62" s="4" t="n">
+        <v>4.40121981373114</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>12.0948145431204</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>7.34149054505007</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B63" s="5" t="n">
-        <v>4.40121981373114</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>12.0948145431204</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>7.34149054505007</v>
+      <c r="B63" s="4" t="n">
+        <v>-1.50785505644588</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>6.05341731768172</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>7.68911917098447</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B64" s="5" t="n">
-        <v>-1.50785505644588</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>6.05341731768172</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>7.68911917098447</v>
+      <c r="B64" s="4" t="n">
+        <v>-3.19012504007695</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>-0.836900767480431</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>2.42927251732101</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="5" t="n">
-        <v>-3.19012504007695</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>-0.836900767480431</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>2.42927251732101</v>
+      <c r="B65" s="4" t="n">
+        <v>3.53535353535352</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>3.08416303671437</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-0.438726284589608</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="5" t="n">
-        <v>3.53535353535352</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>3.08416303671437</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>-0.438726284589608</v>
+      <c r="B66" s="4" t="n">
+        <v>-0.59976009596161</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>-4.91228070175439</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-4.34054398339271</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="5" t="n">
-        <v>-0.59976009596161</v>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>-4.91228070175439</v>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>-4.34054398339271</v>
+      <c r="B67" s="4" t="n">
+        <v>-0.868865647626704</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>-0.194421299051706</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>0.685063253680562</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="5" t="n">
-        <v>-0.868865647626704</v>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>-0.194421299051706</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>0.685063253680562</v>
+      <c r="B68" s="4" t="n">
+        <v>4.87745495861061</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>9.3702790808619</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>4.2808017869739</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="5" t="n">
-        <v>4.87745495861061</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>9.3702790808619</v>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>4.2808017869739</v>
+      <c r="B69" s="4" t="n">
+        <v>-1.32322216203667</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>3.59856057576968</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>4.98583729090627</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="5" t="n">
-        <v>-1.32322216203667</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>3.59856057576968</v>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>4.98583729090627</v>
+      <c r="B70" s="4" t="n">
+        <v>-2.14868255959849</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0.0701729763867842</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>2.27296115831532</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B71" s="5" t="n">
-        <v>-2.14868255959849</v>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>0.0701729763867842</v>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>2.27296115831532</v>
+      <c r="B71" s="4" t="n">
+        <v>1.77111716621252</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>4.30910557133342</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>2.48887683362717</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B72" s="5" t="n">
-        <v>1.77111716621252</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>4.30910557133342</v>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>2.48887683362717</v>
-      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="n">
+        <v>4.45042016806723</v>
+      </c>
+      <c r="D72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5" t="n">
-        <v>4.45042016806723</v>
-      </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4" t="n">
+        <v>1.21323292784965</v>
+      </c>
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B74" s="5"/>
-      <c r="C74" s="5" t="n">
-        <v>1.21323292784965</v>
-      </c>
+      <c r="C74" s="5"/>
       <c r="D74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-    </row>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A75:D78"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A74:D77"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 4.xlsx
+++ b/agriculture 4.xlsx
@@ -20,18 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Area (Million Hectares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production (MT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield (kg./H)</t>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield</t>
   </si>
   <si>
     <t xml:space="preserve">1951-52</t>
@@ -245,6 +245,30 @@
   </si>
   <si>
     <t xml:space="preserve">2021-22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unit:- </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Area - Million Hectares, Product – Metric Ton, Yield – kg./Hector</t>
+    </r>
   </si>
   <si>
     <r>
@@ -307,18 +331,18 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -381,7 +405,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -390,8 +414,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -402,7 +426,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,14 +459,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1048576"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.73"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,1028 +480,1023 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>-0.369913686806411</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2.30224321133412</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2.68293150002872</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-0.369913686806411</v>
+        <v>5.29084158415842</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2.30224321133412</v>
+        <v>13.8680515483747</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.68293150002872</v>
+        <v>8.1462140992167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5.29084158415842</v>
+        <v>6.83710451562345</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.8680515483747</v>
+        <v>17.9391891891892</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>8.1462140992167</v>
+        <v>10.3918052010761</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6.83710451562345</v>
+        <v>-1.10937929769872</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17.9391891891892</v>
+        <v>-2.56373531939271</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>10.3918052010761</v>
+        <v>-1.46999093948198</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-1.10937929769872</v>
+        <v>2.50324494715373</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.56373531939271</v>
+        <v>-1.73452888431576</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.46999093948198</v>
+        <v>-4.13489131641115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2.50324494715373</v>
+        <v>0.524602026049204</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.73452888431576</v>
+        <v>4.50261780104713</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.13489131641115</v>
+        <v>3.95766145704128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.524602026049204</v>
+        <v>-1.49361166096814</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.50261780104713</v>
+        <v>-7.94446034926997</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.95766145704128</v>
+        <v>-6.54968341340801</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-1.49361166096814</v>
+        <v>4.82279868469127</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.94446034926997</v>
+        <v>19.9502410200591</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.54968341340801</v>
+        <v>14.4328492875504</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4.82279868469127</v>
+        <v>0.923666782851162</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>19.9502410200591</v>
+        <v>-0.609281825252783</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.4328492875504</v>
+        <v>-1.51891578274</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.923666782851162</v>
+        <v>-0.207218097047135</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.609281825252783</v>
+        <v>6.97795748010954</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.51891578274</v>
+        <v>7.19961328136802</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>-0.207218097047135</v>
+        <v>1.42758262675204</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.97795748010954</v>
+        <v>0.84125822970007</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.19961328136802</v>
+        <v>-0.577757736317008</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1.42758262675204</v>
+        <v>0.520344621683866</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.84125822970007</v>
+        <v>-3.09515173497762</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.577757736317008</v>
+        <v>-3.59724466366188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.520344621683866</v>
+        <v>-0.356415478615069</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.09515173497762</v>
+        <v>0.611353711790397</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.59724466366188</v>
+        <v>0.971830157609976</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>-0.356415478615069</v>
+        <v>0.58763413387839</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.611353711790397</v>
+        <v>10.8134920634921</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.971830157609976</v>
+        <v>10.1649751736389</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.58763413387839</v>
+        <v>-2.54847176361019</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>10.8134920634921</v>
+        <v>-19.0353625783348</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.1649751736389</v>
+        <v>-16.9182373311481</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>-2.54847176361019</v>
+        <v>0.17376194613381</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-19.0353625783348</v>
+        <v>2.59847961299242</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-16.9182373311481</v>
+        <v>2.42133061821883</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.17376194613381</v>
+        <v>5.30789245446661</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.59847961299242</v>
+        <v>28.0479590462077</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.42133061821883</v>
+        <v>21.5936626281454</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>5.30789245446661</v>
+        <v>-0.815351671882714</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>28.0479590462077</v>
+        <v>-1.09416096791162</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>21.5936626281454</v>
+        <v>-0.281035231598581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>-0.815351671882714</v>
+        <v>2.60732375653905</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.09416096791162</v>
+        <v>5.83980427614084</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.281035231598581</v>
+        <v>3.15006020855217</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2.60732375653905</v>
+        <v>0.606943432872065</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.83980427614084</v>
+        <v>8.96482412060302</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.15006020855217</v>
+        <v>8.30714968765911</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>0.606943432872065</v>
+        <v>-1.36743886743886</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8.96482412060302</v>
+        <v>-2.99760191846523</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.30714968765911</v>
+        <v>-1.65233344799908</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>-1.36743886743886</v>
+        <v>-2.72386233893329</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.99760191846523</v>
+        <v>-7.73984976704384</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.65233344799908</v>
+        <v>-5.15687486154671</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>-2.72386233893329</v>
+        <v>6.08651911468814</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.73984976704384</v>
+        <v>7.8738534473874</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.15687486154671</v>
+        <v>1.68539325842696</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>6.08651911468814</v>
+        <v>-4.31484115694643</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7.8738534473874</v>
+        <v>-4.62405655870832</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.68539325842696</v>
+        <v>-0.322787335130625</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>-4.31484115694643</v>
+        <v>5.86389164188967</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.62405655870832</v>
+        <v>21.236101372333</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.322787335130625</v>
+        <v>14.5203153426319</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>5.86389164188967</v>
+        <v>-2.98018411608676</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>21.236101372333</v>
+        <v>-8.14674047756755</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>14.5203153426319</v>
+        <v>-5.32503018364364</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>-2.98018411608676</v>
+        <v>2.54100997105178</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-8.14674047756755</v>
+        <v>13.7087343707835</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.32503018364364</v>
+        <v>10.8911112602635</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2.54100997105178</v>
+        <v>1.16844416562107</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>13.7087343707835</v>
+        <v>4.34301083775019</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.8911112602635</v>
+        <v>3.13729446181781</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1.16844416562107</v>
+        <v>-2.94550810014728</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.34301083775019</v>
+        <v>-16.8309325246399</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.13729446181781</v>
+        <v>-14.3065336463224</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>-2.94550810014728</v>
+        <v>1.16604105103426</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-16.8309325246399</v>
+        <v>18.1312670920693</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-14.3065336463224</v>
+        <v>16.769200917672</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1.16604105103426</v>
+        <v>1.94994868556089</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>18.1312670920693</v>
+        <v>2.86287522185353</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>16.769200917672</v>
+        <v>0.895361908020154</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1.94994868556089</v>
+        <v>-3.12838779619018</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.86287522185353</v>
+        <v>-2.83570892723181</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.895361908020154</v>
+        <v>0.302264074170933</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>-3.12838779619018</v>
+        <v>4.84412470023981</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.83570892723181</v>
+        <v>17.642063001853</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.302264074170933</v>
+        <v>12.2067360165358</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>4.84412470023981</v>
+        <v>-3.42329978652027</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>17.642063001853</v>
+        <v>-4.48250968038328</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>12.2067360165358</v>
+        <v>-1.0966592350931</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>-3.42329978652027</v>
+        <v>1.06576142733086</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-4.48250968038328</v>
+        <v>3.3667720214374</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-1.0966592350931</v>
+        <v>2.27682184913445</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1.06576142733086</v>
+        <v>-0.640524917981566</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3.3667720214374</v>
+        <v>-4.66631215102367</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2.27682184913445</v>
+        <v>-4.05146664624341</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>-0.640524917981566</v>
+        <v>-5.90408805031447</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-4.66631215102367</v>
+        <v>-2.14056616929298</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-4.05146664624341</v>
+        <v>3.99904214559386</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>-5.90408805031447</v>
+        <v>6.66722366112458</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>-2.14056616929298</v>
+        <v>21.0687566797292</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>3.99904214559386</v>
+        <v>13.5015051892786</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="4" t="n">
-        <v>6.66722366112458</v>
+        <v>-0.704942429701583</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>21.0687566797292</v>
+        <v>0.659133709981163</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>13.5015051892786</v>
+        <v>1.37422704424726</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>-0.704942429701583</v>
+        <v>0.844048276406095</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.659133709981163</v>
+        <v>3.12792329279701</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1.37422704424726</v>
+        <v>2.26427120855013</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>0.844048276406095</v>
+        <v>-4.66989987484355</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>3.12792329279701</v>
+        <v>-4.5410737570157</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2.26427120855013</v>
+        <v>0.135529834682591</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>-4.66989987484355</v>
+        <v>1.05029949946664</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>-4.5410737570157</v>
+        <v>6.59223185651503</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.135529834682591</v>
+        <v>5.48406241857502</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" s="4" t="n">
-        <v>1.05029949946664</v>
+        <v>-0.324807145757211</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>6.59223185651503</v>
+        <v>2.66324938711835</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>5.48406241857502</v>
+        <v>2.99778373964772</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>-0.324807145757211</v>
+        <v>0.90427698574338</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2.66324938711835</v>
+        <v>3.92923043525453</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2.99778373964772</v>
+        <v>2.99780161215109</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46" s="4" t="n">
-        <v>0.90427698574338</v>
+        <v>-2.30098498304537</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>3.92923043525453</v>
+        <v>-5.78590078328982</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2.99780161215109</v>
+        <v>-3.56703964814694</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47" s="4" t="n">
-        <v>-2.30098498304537</v>
+        <v>2.1237914221965</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>-5.78590078328982</v>
+        <v>9.92683737944797</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>-3.56703964814694</v>
+        <v>7.64948522753948</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2.1237914221965</v>
+        <v>0.396504288719846</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>9.92683737944797</v>
+        <v>-3.06055563959059</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>7.64948522753948</v>
+        <v>-3.44797507788162</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49" s="4" t="n">
-        <v>0.396504288719846</v>
+        <v>0.886596276295637</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-3.06055563959059</v>
+        <v>5.90346405908666</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-3.44797507788162</v>
+        <v>4.96947717563854</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" s="4" t="n">
-        <v>0.886596276295637</v>
+        <v>-1.65375089877767</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>5.90346405908666</v>
+        <v>3.04012573056334</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>4.96947717563854</v>
+        <v>4.75388370105798</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="4" t="n">
-        <v>-1.65375089877767</v>
+        <v>-1.66531275385865</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>3.04012573056334</v>
+        <v>-6.19161105815063</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>4.75388370105798</v>
+        <v>-4.5774647887324</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="4" t="n">
-        <v>-1.66531275385865</v>
+        <v>1.42916150351096</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-6.19161105815063</v>
+        <v>8.14999237843606</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-4.5774647887324</v>
+        <v>6.64206642066421</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1.42916150351096</v>
+        <v>-7.26502687734159</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>8.14999237843606</v>
+        <v>-17.8905332393704</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>6.64206642066421</v>
+        <v>-11.4763552479815</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54" s="4" t="n">
-        <v>-7.26502687734159</v>
+        <v>8.42262427542597</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-17.8905332393704</v>
+        <v>21.9831778909424</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-11.4763552479815</v>
+        <v>12.5081433224756</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55" s="4" t="n">
-        <v>8.42262427542597</v>
+        <v>-2.72985014175781</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>21.9831778909424</v>
+        <v>-6.95623622121112</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>12.5081433224756</v>
+        <v>-4.34279096699479</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56" s="4" t="n">
-        <v>-2.72985014175781</v>
+        <v>1.26582278481013</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-6.95623622121112</v>
+        <v>5.16233111514417</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-4.34279096699479</v>
+        <v>3.81355932203389</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57" s="4" t="n">
-        <v>1.26582278481013</v>
+        <v>1.73519736842105</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>5.16233111514417</v>
+        <v>4.16107382550337</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3.81355932203389</v>
+        <v>2.39067055393587</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58" s="4" t="n">
-        <v>1.73519736842105</v>
+        <v>0.291003152534142</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>4.16107382550337</v>
+        <v>6.21318114874816</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>2.39067055393587</v>
+        <v>5.90831435079726</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59" s="4" t="n">
-        <v>0.291003152534142</v>
+        <v>-0.99943580236963</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>6.21318114874816</v>
+        <v>1.5989253834821</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>5.90831435079726</v>
+        <v>2.64820540395214</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60" s="4" t="n">
-        <v>-0.99943580236963</v>
+        <v>-1.22120003256534</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.5989253834821</v>
+        <v>-6.97743847827014</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>2.64820540395214</v>
+        <v>-5.81456259821896</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61" s="4" t="n">
-        <v>-1.22120003256534</v>
+        <v>4.40121981373114</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-6.97743847827014</v>
+        <v>12.0948145431204</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-5.81456259821896</v>
+        <v>7.34149054505007</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62" s="4" t="n">
-        <v>4.40121981373114</v>
+        <v>-1.50785505644588</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>12.0948145431204</v>
+        <v>6.05341731768172</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>7.34149054505007</v>
+        <v>7.68911917098447</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63" s="4" t="n">
-        <v>-1.50785505644588</v>
+        <v>-3.19012504007695</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>6.05341731768172</v>
+        <v>-0.836900767480431</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>7.68911917098447</v>
+        <v>2.42927251732101</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64" s="4" t="n">
-        <v>-3.19012504007695</v>
+        <v>3.53535353535352</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.836900767480431</v>
+        <v>3.08416303671437</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>2.42927251732101</v>
+        <v>-0.438726284589608</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65" s="4" t="n">
-        <v>3.53535353535352</v>
+        <v>-0.59976009596161</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>3.08416303671437</v>
+        <v>-4.91228070175439</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>-0.438726284589608</v>
+        <v>-4.34054398339271</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66" s="4" t="n">
-        <v>-0.59976009596161</v>
+        <v>-0.868865647626704</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-4.91228070175439</v>
+        <v>-0.194421299051706</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-4.34054398339271</v>
+        <v>0.685063253680562</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67" s="4" t="n">
-        <v>-0.868865647626704</v>
+        <v>4.87745495861061</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.194421299051706</v>
+        <v>9.3702790808619</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>0.685063253680562</v>
+        <v>4.2808017869739</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68" s="4" t="n">
-        <v>4.87745495861061</v>
+        <v>-1.32322216203667</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>9.3702790808619</v>
+        <v>3.59856057576968</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>4.2808017869739</v>
+        <v>4.98583729090627</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69" s="4" t="n">
-        <v>-1.32322216203667</v>
+        <v>-2.14868255959849</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>3.59856057576968</v>
+        <v>0.0701729763867842</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>4.98583729090627</v>
+        <v>2.27296115831532</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" s="4" t="n">
-        <v>-2.14868255959849</v>
+        <v>1.77111716621252</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.0701729763867842</v>
+        <v>4.30910557133342</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2.27296115831532</v>
+        <v>2.48887683362717</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>1.77111716621252</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B71" s="4"/>
       <c r="C71" s="4" t="n">
-        <v>4.30910557133342</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>2.48887683362717</v>
-      </c>
+        <v>4.45042016806723</v>
+      </c>
+      <c r="D71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="n">
-        <v>4.45042016806723</v>
+        <v>1.21323292784965</v>
       </c>
       <c r="D72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4" t="n">
-        <v>1.21323292784965</v>
-      </c>
-      <c r="D73" s="4"/>
+    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-    </row>
+      <c r="A74" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="H74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A74:D77"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
